--- a/astro-site/public/dl/kit-tareas/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas/02-partidas-cocina.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calientes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Fríos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mise en Place" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calientes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fríos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mise en Place" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Calientes'!$A$1:$G$36</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Fríos'!$A$1:$G$32</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Mise en Place'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calientes'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Calientes'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Fríos'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Fríos'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mise en Place'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mise en Place'!$A$1:$G$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -117,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -139,48 +142,107 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -540,15 +602,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -556,6 +619,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -563,9 +627,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -594,9 +656,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -604,8 +664,33 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -614,18 +699,18 @@
   <sheetPr>
     <tabColor rgb="00F44336"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -642,10 +727,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -670,7 +756,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -685,18 +771,16 @@
           <t xml:space="preserve">  ANTES DEL SERVICIO</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="19" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -722,10 +806,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -751,10 +833,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -780,10 +860,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -809,10 +887,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -838,10 +914,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -867,10 +941,8 @@
       <c r="G11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -896,10 +968,8 @@
       <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -924,24 +994,23 @@
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="8" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE EL SERVICIO</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="19" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -967,10 +1036,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -996,10 +1063,8 @@
       <c r="G17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1025,10 +1090,8 @@
       <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1054,10 +1117,8 @@
       <c r="G19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1082,24 +1143,23 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="8" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  DESPUÉS DEL SERVICIO</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="19" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="20" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1125,10 +1185,8 @@
       <c r="G23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1154,10 +1212,8 @@
       <c r="G24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="20" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1183,10 +1239,8 @@
       <c r="G25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1212,10 +1266,8 @@
       <c r="G26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1241,10 +1293,8 @@
       <c r="G27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="20" t="n">
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -1270,10 +1320,8 @@
       <c r="G28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="20" t="n">
+        <v>20</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -1298,6 +1346,8 @@
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="8" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
@@ -1306,17 +1356,19 @@
       </c>
       <c r="D32" s="15">
         <f>COUNTIF(F5:F30,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F32" s="15" t="n">
-        <v>20</v>
-      </c>
-    </row>
+      <c r="F32" s="15">
+        <f>COUNTIF(B5:B30,"?*")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
@@ -1324,13 +1376,17 @@
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="19" t="n"/>
       <c r="E34" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F34" s="8" t="n"/>
-    </row>
+      <c r="G34" s="19" t="n"/>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
@@ -1349,13 +1405,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G30">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1364,18 +1433,18 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1392,10 +1461,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1420,7 +1490,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1435,18 +1505,16 @@
           <t xml:space="preserve">  ANTES DEL SERVICIO</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="19" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1472,10 +1540,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1501,10 +1567,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1530,10 +1594,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1559,10 +1621,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1588,10 +1648,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1617,10 +1675,8 @@
       <c r="G11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1645,24 +1701,23 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="8" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE EL SERVICIO</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="19" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1688,10 +1743,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1717,10 +1770,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1746,10 +1797,8 @@
       <c r="G17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1774,24 +1823,23 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="8" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  DESPUÉS DEL SERVICIO</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="19" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1817,10 +1865,8 @@
       <c r="G21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1846,10 +1892,8 @@
       <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="20" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1875,10 +1919,8 @@
       <c r="G23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1904,10 +1946,8 @@
       <c r="G24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="20" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1932,6 +1972,8 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="8" t="n"/>
     </row>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
@@ -1940,17 +1982,19 @@
       </c>
       <c r="D28" s="15">
         <f>COUNTIF(F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28" s="15" t="n">
-        <v>16</v>
-      </c>
-    </row>
+      <c r="F28" s="15">
+        <f>COUNTIF(B5:B26,"?*")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
@@ -1958,13 +2002,17 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n"/>
       <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F30" s="8" t="n"/>
-    </row>
+      <c r="G30" s="19" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
@@ -1977,19 +2025,32 @@
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="F30:G30"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A28:C28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F21 F22 F23 F24 F25" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1998,18 +2059,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2026,10 +2087,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2054,7 +2116,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2069,18 +2131,16 @@
           <t xml:space="preserve">  PROTEÍNAS</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="19" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2106,10 +2166,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2135,10 +2193,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2164,10 +2220,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2192,24 +2246,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="8" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  VEGETALES Y GUARNICIONES</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="19" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -2235,10 +2288,8 @@
       <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -2264,10 +2315,8 @@
       <c r="G13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2293,10 +2342,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2322,10 +2369,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2351,10 +2396,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2379,24 +2422,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="8" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALSAS Y BASES</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="19" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2422,10 +2464,8 @@
       <c r="G20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -2451,10 +2491,8 @@
       <c r="G21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2480,10 +2518,8 @@
       <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="20" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2508,24 +2544,23 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="8" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  POSTRES</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="19" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -2551,10 +2586,8 @@
       <c r="G26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="20" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -2580,10 +2613,8 @@
       <c r="G27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="20" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -2609,10 +2640,8 @@
       <c r="G28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -2637,6 +2666,8 @@
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="8" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
@@ -2645,17 +2676,19 @@
       </c>
       <c r="D32" s="15">
         <f>COUNTIF(F5:F30,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F32" s="15" t="n">
-        <v>18</v>
-      </c>
-    </row>
+      <c r="F32" s="15">
+        <f>COUNTIF(B5:B30,"?*")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
@@ -2663,13 +2696,17 @@
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="19" t="n"/>
       <c r="E34" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F34" s="8" t="n"/>
-    </row>
+      <c r="G34" s="19" t="n"/>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
@@ -2680,21 +2717,34 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G30">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas/02-partidas-cocina.xlsx
@@ -13,12 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mise en Place" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calientes'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Calientes'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Calientes'!$A$1:$G$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Fríos'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Fríos'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Fríos'!$A$1:$G$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mise en Place'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mise en Place'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mise en Place'!$A$1:$G$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,8 +100,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +132,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -190,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -227,6 +252,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -604,79 +684,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Tareas por Partida de Cocina — Restaurante Casual</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Cómo usar estas plantillas</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>▸ Cada pestaña corresponde a una partida o estación de cocina</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>▸ Las tareas están organizadas: antes, durante y después del servicio</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>▸ El chef de partida es responsable de completar y firmar</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>▸ Personaliza añadiendo los platos específicos de tu carta</t>
         </is>
       </c>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="12"/>
-    <row r="13">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>▸ Estás en 02-partidas-cocina.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="35" customHeight="1">
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -701,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -751,7 +949,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -766,652 +964,740 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANTES DEL SERVICIO</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="19" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Encender y precalentar plancha, fogones, horno</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="31" t="n"/>
+      <c r="G6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Preparar fondos y salsas base</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Mise en place: proteínas porcionadas y temperadas</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Mise en place: guarniciones calientes listas</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Verificar stock de aceite para fritura</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Probar temperatura de aceite de freidora</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Organizar mesa de pase con platos calientes</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Probar sazón de todos los platos calientes</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Jefe de Cocina</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="8" t="n"/>
-    </row>
-    <row r="14"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="32" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="33" t="n"/>
+      <c r="E14" s="33" t="n"/>
+      <c r="F14" s="33" t="n"/>
+      <c r="G14" s="33" t="n"/>
+    </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE EL SERVICIO</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="19" t="n"/>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="26" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Mantener limpieza continua de estación</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="32" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Control de tiempos de cocción por comanda</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Reponer mise en place según se agote</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="32" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Comunicar 86s (productos agotados) a sala</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Control de temperatura de mantenimiento (&gt;65°C)</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Control de temperatura de mantenimiento en caliente (≥ 65 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="8" t="n"/>
-    </row>
-    <row r="21"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="32" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="33" t="n"/>
+      <c r="C21" s="33" t="n"/>
+      <c r="D21" s="33" t="n"/>
+      <c r="E21" s="33" t="n"/>
+      <c r="F21" s="33" t="n"/>
+      <c r="G21" s="33" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  DESPUÉS DEL SERVICIO</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="19" t="n"/>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="26" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="n">
+      <c r="A23" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>Guardar proteínas sobrantes: etiquetar y fechar</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Guardar salsas: etiquetar y fechar</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="32" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="n">
+      <c r="A25" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Limpiar plancha con rasqueta y producto específico</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="F25" s="31" t="n"/>
+      <c r="G25" s="32" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Limpiar fogones y quemadores</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="8" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="32" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="n">
+      <c r="A27" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Filtrar y/o cambiar aceite de freidora</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>Apagar la freidora al terminar y filtrar el aceite SÓLO por debajo de 40 °C, nunca en caliente, con guantes y recipiente estable; el aceite usado, al bidón del gestor autorizado</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="8" t="n"/>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="32" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="n">
+      <c r="A28" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>Limpiar mesa de pase</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="8" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="32" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="n">
+      <c r="A29" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>Anotar las mermas del turno (producto, cantidad y motivo)</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>Chef partida</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="32" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>Dejar partida lista para el siguiente turno</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="8" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="32" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="n"/>
+      <c r="B31" s="35" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="30" t="n"/>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="32" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="34" t="n"/>
+      <c r="B32" s="35" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="30" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="32" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="n"/>
+      <c r="B33" s="35" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="30" t="n"/>
+      <c r="F33" s="31" t="n"/>
+      <c r="G33" s="32" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="n"/>
+      <c r="B34" s="35" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="32" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="n"/>
+      <c r="B35" s="35" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="30" t="n"/>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="32" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D32" s="15">
-        <f>COUNTIF(F5:F30,"✓")</f>
+      <c r="D37" s="15">
+        <f>COUNTIFS(B5:B35,"?*",F5:F35,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>COUNTIF(B5:B30,"?*")</f>
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="F37" s="15">
+        <f>COUNTIF(B5:B35,"?*")-COUNTIF(F5:F35,"N/A")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="B39" s="36" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="19" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="F39" s="36" t="n"/>
+      <c r="G39" s="19" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="F39:G39"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G30">
+  <conditionalFormatting sqref="A5:G35">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1435,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1485,7 +1771,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1500,544 +1786,632 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANTES DEL SERVICIO</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="19" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Lavar y desinfectar lechugas y vegetales</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Lavar y desinfectar hojas verdes y vegetales de consumo crudo con lejía apta para uso alimentario según la dosis del fabricante (habitual: 70 ppm, 5 min) y ACLARAR con agua potable abundante</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="31" t="n"/>
+      <c r="G6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Preparar vinagretas y aliños del día</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Mise en place: cortar vegetales y frutas</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Preparar bases de ensalada</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Pescado para consumo crudo o semicrudo (tartar, ceviche, carpaccio) — prevención de ANISAKIS: confirmar congelación previa ≥24 h a −20 °C (o −35 °C 15 h) y anotar el lote</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>Chef partida</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="32" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Porcionar carpaccios, ceviches, tartares</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="32" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Verificar stock de productos fríos en cámara</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="32" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Montar estación fría con inserts organizados</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="8" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="32" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="33" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="33" t="n"/>
+      <c r="E14" s="33" t="n"/>
+      <c r="F14" s="33" t="n"/>
+      <c r="G14" s="33" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE EL SERVICIO</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="26" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Montar ensaladas y platos fríos al momento</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Mantener temperatura de exposición &lt; 8°C</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="32" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Mantener la exposición a ≤ 4 °C para crudos de pescado y marisco; &lt; 8 °C para vegetales y ensaladas</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="32" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Reponer inserts de vegetales según se agoten</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="32" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Limpiar estación entre servicios</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="8" t="n"/>
-    </row>
-    <row r="19"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="32" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="33" t="n"/>
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  DESPUÉS DEL SERVICIO</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n"/>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="19" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="26" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Guardar vegetales cortados: tapar y fechar</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="32" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>Guardar vinagretas y aliños en cámara</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="32" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Desechar hojas marchitas y producto deteriorado</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="32" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Limpiar y desinfectar estación fría</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="F25" s="31" t="n"/>
+      <c r="G25" s="32" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Limpiar tablas de corte (verde = vegetales)</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="8" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="32" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="n"/>
+      <c r="B27" s="35" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="30" t="n"/>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="32" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="34" t="n"/>
+      <c r="B28" s="35" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="30" t="n"/>
+      <c r="E28" s="30" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="32" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="n"/>
+      <c r="B29" s="35" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="30" t="n"/>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="32" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="n"/>
+      <c r="B30" s="35" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="30" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="32" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="n"/>
+      <c r="B31" s="35" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="30" t="n"/>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="32" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D28" s="15">
-        <f>COUNTIF(F5:F26,"✓")</f>
+      <c r="D33" s="15">
+        <f>COUNTIFS(B5:B31,"?*",F5:F31,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28" s="15">
-        <f>COUNTIF(B5:B26,"?*")</f>
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="F33" s="15">
+        <f>COUNTIF(B5:B31,"?*")-COUNTIF(F5:F31,"N/A")</f>
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="B35" s="36" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="19" t="n"/>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="19" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="F35:G35"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G26">
+  <conditionalFormatting sqref="A5:G31">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2061,7 +2435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2126,613 +2500,709 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PROTEÍNAS</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="19" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Carne roja: porcionada, temperada</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="31" t="n"/>
+      <c r="G6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Aves: porcionadas, marinadas si aplica</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Pescado: limpio, porcionado, en frío</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Marisco: limpio, desvenado si aplica</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>Chef partida</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
-    </row>
-    <row r="10"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="32" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Pescado y marisco para consumo crudo o semicrudo — prevención de ANISAKIS: confirmar congelación previa ≥24 h a −20 °C (o −35 °C 15 h) y anotar el lote</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>Chef partida</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="32" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="33" t="n"/>
+      <c r="B11" s="33" t="n"/>
+      <c r="C11" s="33" t="n"/>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="n"/>
+      <c r="F11" s="33" t="n"/>
+      <c r="G11" s="33" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  VEGETALES Y GUARNICIONES</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="19" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Patatas: peladas, cortadas, en agua</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="32" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Cebolla: brunoise, juliana, aros</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="32" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>Ajo: pelado, laminado, picado</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="32" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Tomate: concassé, rodajas, gajos</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="32" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Verduras variadas según carta</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="32" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Hierbas frescas: lavadas, picadas</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="32" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="33" t="n"/>
+      <c r="C19" s="33" t="n"/>
+      <c r="D19" s="33" t="n"/>
+      <c r="E19" s="33" t="n"/>
+      <c r="F19" s="33" t="n"/>
+      <c r="G19" s="33" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALSAS Y BASES</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="19" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="26" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>Fondo oscuro / claro: caliente y listo</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="F21" s="31" t="n"/>
+      <c r="G21" s="32" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Salsas del día preparadas</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="32" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>Vinagretas y aliños</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="32" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Mayonesas y emulsiones</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="32" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="33" t="n"/>
+      <c r="B25" s="33" t="n"/>
+      <c r="C25" s="33" t="n"/>
+      <c r="D25" s="33" t="n"/>
+      <c r="E25" s="33" t="n"/>
+      <c r="F25" s="33" t="n"/>
+      <c r="G25" s="33" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  POSTRES</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="19" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>Postres del día emplatados o listos para emplatar</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>Pastelero</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Helados temperados (pasar de -18 a -12°C)</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="32" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>Helados temperados (pasar de −18 a −12 °C)</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>Pastelero</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="32" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>Salsas dulces y coulis listos</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>Pastelero</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="32" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="27" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>Decoración de postres preparada</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>Pastelero</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="8" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="32" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="n"/>
+      <c r="B31" s="35" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="30" t="n"/>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="32" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="34" t="n"/>
+      <c r="B32" s="35" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="30" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="32" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="n"/>
+      <c r="B33" s="35" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="30" t="n"/>
+      <c r="F33" s="31" t="n"/>
+      <c r="G33" s="32" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="n"/>
+      <c r="B34" s="35" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="32" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="n"/>
+      <c r="B35" s="35" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="30" t="n"/>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="32" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D32" s="15">
-        <f>COUNTIF(F5:F30,"✓")</f>
+      <c r="D37" s="15">
+        <f>COUNTIFS(B5:B35,"?*",F5:F35,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>COUNTIF(B5:B30,"?*")</f>
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="F37" s="15">
+        <f>COUNTIF(B5:B35,"?*")-COUNTIF(F5:F35,"N/A")</f>
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="B39" s="36" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="19" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="F39" s="36" t="n"/>
+      <c r="G39" s="19" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F39:G39"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G30">
+  <conditionalFormatting sqref="A5:G35">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/astro-site/public/dl/kit-tareas/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas/02-partidas-cocina.xlsx
@@ -766,6 +766,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="22" t="inlineStr">
         <is>
@@ -773,6 +774,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="32" customHeight="1">
       <c r="B19" s="23" t="inlineStr">
         <is>
@@ -787,6 +789,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="22" t="inlineStr">
         <is>
@@ -794,6 +797,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="32" customHeight="1">
       <c r="B24" s="23" t="inlineStr">
         <is>
@@ -808,6 +812,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="22" t="inlineStr">
         <is>
@@ -815,10 +820,11 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
+    <row r="28"/>
+    <row r="29" ht="16" customHeight="1">
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
         </is>
       </c>
     </row>
@@ -836,10 +842,10 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
+    <row r="32" ht="48" customHeight="1">
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
         </is>
       </c>
     </row>
@@ -850,6 +856,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="22" t="inlineStr">
         <is>
@@ -857,6 +864,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37" ht="35" customHeight="1">
       <c r="B37" s="22" t="inlineStr">
         <is>
@@ -871,6 +879,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="22" t="inlineStr">
         <is>
@@ -1685,10 +1694,10 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="B39:D39"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G35">
@@ -1697,7 +1706,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2397,8 +2406,8 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
     <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A21:G21"/>
@@ -2411,7 +2420,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3190,9 +3199,9 @@
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A37:C37"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A37:C37"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="B39:D39"/>
   </mergeCells>
@@ -3202,7 +3211,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
